--- a/content/post/drafts/season-prediction/ladies_simple-model-tests-r2.xlsx
+++ b/content/post/drafts/season-prediction/ladies_simple-model-tests-r2.xlsx
@@ -610,25 +610,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.493160991833125</v>
+        <v>0.489101071221495</v>
       </c>
       <c r="C9" t="n">
-        <v>0.47634711305188</v>
+        <v>0.49219911121298</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0523038815524186</v>
+        <v>0.0596915127542702</v>
       </c>
       <c r="E9" t="n">
-        <v>0.173916442682154</v>
+        <v>0.152432513798556</v>
       </c>
       <c r="F9" t="n">
-        <v>0.477756990518565</v>
+        <v>0.472590207491905</v>
       </c>
       <c r="G9" t="n">
-        <v>0.474653533927077</v>
+        <v>0.530550210288717</v>
       </c>
       <c r="H9" t="n">
-        <v>0.358023158927537</v>
+        <v>0.36609410446132</v>
       </c>
     </row>
     <row r="10">
